--- a/data/wordstat_queue.xlsx
+++ b/data/wordstat_queue.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,741 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 гидравлическая часть</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 с электронной платой</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Корпус фильтра EA888 +Магнит на корпус фильтра EA888 3 gen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Оригинал Volkswagen сепараторная пластина + пластины на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Оригинал Volkswagen пластины на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Пластины на соленоиды мехатроника DQ200 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Соленоид регулятор давления DQ200 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 DSG7 проверен на стенде и на АВТО</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Усиленная плита dsg7 dq200 + фильтр</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Корпус фильтра EA888</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Магнит на корпус фильтра EA888 3 gen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Масляный фильтр DQ500 0BH DSG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра 02E305045 DSG6 DQ250+фильтр 02e305051C</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>поршень штока усиленный DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>усиленный Ремкомплект штока DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Планка соленоидов DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина ОРИГИНАЛ мехатроника DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>втулка (гильза) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.6 л</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E 1.8 л</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника + прокладка поддона комплект</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники Volkswagen сравнение</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка на соленоиды 0B5 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Клипса пыльника штока мехатроника DSG7 DQ200 0am 0cw</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ОРИГИНАЛ Фильтр-сетка на соленоиды 0B5 DSG7</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>импульсное кольцо распредвала Opel Chevrolet</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра DQ250 02E</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Прокладка Эл. Платы 0AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Прокладка эл. платы DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы поштучно</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Прокладки платы DSG7 маленькие</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ремкомплект (прокладки) улучшенный</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Что происходит с дешевыми резинками и некачественными вставками мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>сравнение фильстров</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2 шт Планки соленоидов DSG7 DQ200 на весь комплект</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Мехатроник с платой 02E927770AL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Соленоиды 6T30 6T40 6T45</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Усиленная плита + качественный фильтр + оригинальные сальники комплектом дешевле!</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Усиленная плита + качественный фильтр + пыльники Оригинал комплектом дешевле!</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Усиленная плита + качественный фильтр + сальники оригинал комплектом дешевле!</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DQ200 улучшенный!</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2 карточка описание комплекта накладок на педали</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник сравнение</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Сальник привода (левый)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Сальник привода (правый)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>комплект накладок на педали</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>сальник входного вала</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>сальник первичного вала</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Заглушка DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6 и задней передачи DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Подшипники вилки 6 и задней передачи DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника 2 шт DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Стальная вставка плиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Фильтр мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>клипсы штоков мехатроника DSG7 DQ200 2 шт комплект на 2 штока</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор Оригинал VAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG7 DQ200 с Эл. Платой, проверен на авто</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Новый оригинальный гидроаккумулятор мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Оригинальный комплект пыльников штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Оригинальный комплект сальников штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Прокладка Эл. Блока Управления DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Прокладка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/wordstat_queue.xlsx
+++ b/data/wordstat_queue.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Очередь" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="На проверку" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Очередь'!$A$1:$B$106</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +34,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +49,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,11 +69,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,8 +445,8 @@
   <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,737 +462,1409 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Длинные 101 мм Штоки 0am325091E усиленные с доп. резинкой 2шт + 2шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Длинные 101 мм Штоки 0am325091E усиленный доп. резинкой + новая втулка (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Короткие 99мм штоки 0am325091F усиленные с доп. резинкой 2 шт+2 шт новые втулки (гильзы) Без задиров и царапин DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>штоки dq200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Короткий 99мм шток 0am325091F усиленныей с доп. резинкой + новые втулки (гильзы) мехатроника без задиров и царапин DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DSG7 DQ500 0BH325159</t>
         </is>
       </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 гидравлическая часть</t>
         </is>
       </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 с электронной платой</t>
         </is>
       </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
         </is>
       </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>электронная плата dq200</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Volkswagen пластина 1шт на соленоиды мехатроника DQ200 DSG7</t>
         </is>
       </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра EA888 +Магнит на корпус фильтра EA888 3 gen</t>
         </is>
       </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>корпус фильтра ea888</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Оригинал Volkswagen сепараторная пластина + пластины на соленоиды мехатроника DQ200 DSG7</t>
         </is>
       </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>сепараторная пластина dq200</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Оригинал Volkswagen пластины на соленоиды мехатроника DQ200 DSG7</t>
         </is>
       </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>пластины на соленоиды dq200</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Пластины на соленоиды мехатроника DQ200 DSG7</t>
         </is>
       </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>пластины на соленоиды dq200</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Соленоид регулятор давления DQ200 DSG7</t>
         </is>
       </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>соленоид регулятор давления dq200</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Крышка мехатроника DQ200 DSG7 ОРИГИНАЛ W</t>
         </is>
       </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DQ200 DSG7 проверен на стенде и на АВТО</t>
         </is>
       </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Болт мехатроника Длинный DSG7 DQ200 WHT001922</t>
         </is>
       </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>болт мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Болт мехатроника Короткий DSG7 DQ200 01x301127C</t>
         </is>
       </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>болт мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита dsg7 dq200 + фильтр</t>
         </is>
       </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>плита dq200</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита мехатроника DSG7 DQ200 фильтр + пыльники + сальники</t>
         </is>
       </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита мехатроника DSG7 DQ200 + фильтр + пыльники</t>
         </is>
       </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Корпус фильтра EA888</t>
         </is>
       </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>корпус фильтра ea888</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Магнит на корпус фильтра EA888 3 gen</t>
         </is>
       </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>корпус фильтра ea888</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Масляный фильтр DQ500 0BH DSG</t>
         </is>
       </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>фильтр dq500</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Усиленная плита мехатроника+качественный фильтр DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DSG6 DQ250 02E305045</t>
         </is>
       </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра 02E305045 DSG6 DQ250+фильтр 02e305051C</t>
         </is>
       </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DSG7 DQ500 0BH325159+фильтр 0BH325183B</t>
         </is>
       </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq500</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Усиленная прокладка крышки мехатроника DQ200 с утолщением</t>
         </is>
       </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>поршень штока усиленный DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>усиленный Ремкомплект штока DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Крышка штока мехатроника DSG7 DQ200 0am 0cw</t>
         </is>
       </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Планка соленоидов DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>планка соленоидов dq200</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Сальник штока мехатроника DSG7 DQ200 0am 0cw</t>
         </is>
       </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Сепараторная пластина мехатроника DQ200</t>
         </is>
       </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>сепараторная пластина dq200</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Сепараторная пластина ОРИГИНАЛ мехатроника DQ200</t>
         </is>
       </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>сепараторная пластина dq200</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>втулка (гильза) мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>сепараторная пластина dq200</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E 1.6 л</t>
         </is>
       </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Гидроблок JF015E 1.8 л</t>
         </is>
       </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>гидроблок jf015e</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>ДОПОЛНИТЕЛЬНЫЙ АЛЮМИНИЕВЫЙ САЛЬНИК ТОЛКАТЕЛЯ DSG7 DQ20</t>
         </is>
       </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Крышка мехатроника + прокладка поддона комплект</t>
         </is>
       </c>
+      <c r="B44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 + усиленная прокладка (утолщённая версия)</t>
         </is>
       </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Оригинальные сальники Volkswagen сравнение</t>
         </is>
       </c>
+      <c r="B46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Оригинальный (VAG) ремкомплект штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока DSG7 DQ200 VAG</t>
         </is>
       </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Фильтр-сетка на соленоиды 0B5 DSG7</t>
         </is>
       </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>фильтр-сетка dq500</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Клипса пыльника штока мехатроника DSG7 DQ200 0am 0cw</t>
         </is>
       </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>клипса пыльника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>ОРИГИНАЛ Фильтр-сетка на соленоиды 0B5 DSG7</t>
         </is>
       </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>фильтр-сетка dq500</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект штока DSG7 DQ200 (крышка, пыльник, сальник)</t>
         </is>
       </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>импульсное кольцо распредвала Opel Chevrolet</t>
         </is>
       </c>
+      <c r="B55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DQ250 02E</t>
         </is>
       </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>корпус масляного фильтра dq250</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Прокладка Эл. Платы 0AM</t>
         </is>
       </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>эл. платы dq200</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Прокладка эл. платы DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>эл. платы dq200</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Прокладка электронной платы поштучно</t>
         </is>
       </c>
+      <c r="B61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Прокладки платы DSG7 маленькие</t>
         </is>
       </c>
+      <c r="B62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект штока DSG 7 DQ200 пыльник + сальник + крышка</t>
         </is>
       </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>сальник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>ремкомплект (прокладки) улучшенный</t>
         </is>
       </c>
+      <c r="B64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Что происходит с дешевыми резинками и некачественными вставками мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>полный комплект прокладок на электронную плату мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>сравнение фильстров</t>
         </is>
       </c>
+      <c r="B67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>2 шт Планки соленоидов DSG7 DQ200 на весь комплект</t>
         </is>
       </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>планки соленоидов dq200</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Втулки (гильзы) 2 шт комплект штоков DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>шток dq200</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Мехатроник с платой 02E927770AL</t>
         </is>
       </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq250</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Соленоиды 6T30 6T40 6T45</t>
         </is>
       </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>соленоиды 6t40</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Усиленная плита + качественный фильтр + оригинальные сальники комплектом дешевле!</t>
         </is>
       </c>
+      <c r="B72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Усиленная плита + качественный фильтр + пыльники Оригинал комплектом дешевле!</t>
         </is>
       </c>
+      <c r="B73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Усиленная плита + качественный фильтр + сальники оригинал комплектом дешевле!</t>
         </is>
       </c>
+      <c r="B74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Фильтр мехатроника DQ200 улучшенный!</t>
         </is>
       </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>2 карточка описание комплекта накладок на педали</t>
         </is>
       </c>
+      <c r="B76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>крышка мехатроника dq200</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Оригинальный сальник сравнение</t>
         </is>
       </c>
+      <c r="B79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Сальник привода (левый)</t>
         </is>
       </c>
+      <c r="B80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Сальник привода (правый)</t>
         </is>
       </c>
+      <c r="B81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Сальники толкателей вилок мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Толкатели вилок мехатроника DSG7 DQ200 + сальники + усиленные алюминиевые сальники с гальваническим покрытием</t>
         </is>
       </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>комплект накладок на педали</t>
         </is>
       </c>
+      <c r="B84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>комплект толкателей вилок (поршней) 4шт+сальники 4 шт DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>сальники dq200</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>комплект толкателей вилок (поршней) мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>полный комплект сальников толкателей вилок мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>сальник входного вала</t>
         </is>
       </c>
+      <c r="B88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>сальник первичного вала</t>
         </is>
       </c>
+      <c r="B89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>усиленные алюминиевые сальники толкателя с гальваническим покрытием мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Заглушка DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>заглушка dq200</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Комплект болтов мехатроника DSG7 DQ200 (7 шт)</t>
         </is>
       </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Подшипник вилки 6 и задней передачи DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>подшипник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Подшипники вилки 6 и задней передачи DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>подшипники dq200</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Сальники штоков мехатроника 2 шт DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Стальная вставка плиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>стальная вставка dq200</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Фильтр мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>клипсы штоков мехатроника DSG7 DQ200 2 шт комплект на 2 штока</t>
         </is>
       </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Гидроаккумулятор Оригинал VAG</t>
         </is>
       </c>
+      <c r="B100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 с Эл. Платой, проверен на авто</t>
         </is>
       </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Новый оригинальный гидроаккумулятор мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>гидроаккумулятор dq200</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Оригинальный комплект пыльников штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Оригинальный комплект сальников штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Прокладка Эл. Блока Управления DSG7 DQ200</t>
         </is>
       </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>эл. блока dq200</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Прокладка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>мехатроник dq200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B106"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Артикул</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Почему нужна проверка</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника + прокладка поддона комплект</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники Volkswagen сравнение</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>похоже на текст статьи/сравнения, а не на товар — уточните, что это</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>импульсное кольцо распредвала Opel Chevrolet</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы поштучно</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Прокладки платы DSG7 маленькие</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ремкомплект (прокладки) улучшенный</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Что происходит с дешевыми резинками и некачественными вставками мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>похоже на текст статьи/сравнения, а не на товар — уточните, что это</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>сравнение фильстров</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>похоже на текст статьи/сравнения, а не на товар — уточните, что это</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + качественный фильтр + оригинальные сальники комплектом дешевле!</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + качественный фильтр + пыльники Оригинал комплектом дешевле!</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Усиленная плита + качественный фильтр + сальники оригинал комплектом дешевле!</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2 карточка описание комплекта накладок на педали</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>похоже на текст статьи/сравнения, а не на товар — уточните, что это</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник сравнение</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>похоже на текст статьи/сравнения, а не на товар — уточните, что это</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Сальник привода (левый)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Сальник привода (правый)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор Оригинал VAG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>не нашёл код коробки/агрегата в названии — не знаю, к какой платформе относить</t>
         </is>
       </c>
     </row>

--- a/data/wordstat_queue.xlsx
+++ b/data/wordstat_queue.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -195,8 +195,14 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -399,6 +405,11 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
       </patternFill>
     </fill>
   </fills>
@@ -656,7 +667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -665,6 +676,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,6 +1095,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/data/wordstat_queue.xlsx
+++ b/data/wordstat_queue.xlsx
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>штоки dq200; штоки dsg7 dq200; штоки dsg7</t>
+          <t>штоки dq200; штоки dsg7 dq200; штоки dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; штоки dq200 дсг7; штоки dq200 dsg 7; штоки dq200 дсг 7; штоки дсг7; штоки dsg 7; штоки дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>штоки dq200; штоки dsg7 dq200; штоки dsg7</t>
+          <t>штоки dq200; штоки dsg7 dq200; штоки dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; штоки dq200 дсг7; штоки dq200 dsg 7; штоки dq200 дсг 7; штоки дсг7; штоки dsg 7; штоки дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>корпус масляного фильтра dq500; корпус масляного фильтра dsg7 dq500</t>
+          <t>корпус масляного фильтра dq500; корпус масляного фильтра dsg7 dq500; прокладки dq500; прокладки dsg7; ремкомплект dq500; ремкомплект dsg7; запчасти мехатроника dq500; запчасти мехатроника dsg7; корпус масляного фильтра dq500 дсг7; корпус масляного фильтра dq500 dsg 7; корпус масляного фильтра dq500 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>электронная плата dq200; электронная плата dsg7 dq200; электронная плата dsg7</t>
+          <t>электронная плата dq200; электронная плата dsg7 dq200; электронная плата dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; электронная плата dq200 дсг7; электронная плата dq200 dsg 7; электронная плата dq200 дсг 7; электронная плата дсг7; электронная плата dsg 7; электронная плата дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7</t>
+          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сепараторная пластина dq200 дсг7; сепараторная пластина dq200 dsg 7; сепараторная пластина dq200 дсг 7; сепараторная пластина дсг7; сепараторная пластина dsg 7; сепараторная пластина дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>пластины на соленоиды dq200; пластины на соленоиды dsg7 dq200; пластины на соленоиды dsg7</t>
+          <t>пластины на соленоиды dq200; пластины на соленоиды dsg7 dq200; пластины на соленоиды dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; пластины на соленоиды dq200 дсг7; пластины на соленоиды dq200 dsg 7; пластины на соленоиды dq200 дсг 7; пластины на соленоиды дсг7; пластины на соленоиды dsg 7; пластины на соленоиды дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>пластины на соленоиды dq200; пластины на соленоиды dsg7 dq200; пластины на соленоиды dsg7</t>
+          <t>пластины на соленоиды dq200; пластины на соленоиды dsg7 dq200; пластины на соленоиды dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; пластины на соленоиды dq200 дсг7; пластины на соленоиды dq200 dsg 7; пластины на соленоиды dq200 дсг 7; пластины на соленоиды дсг7; пластины на соленоиды dsg 7; пластины на соленоиды дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>соленоид регулятор давления dq200; соленоид регулятор давления dsg7 dq200; соленоид регулятор давления dsg7</t>
+          <t>соленоид регулятор давления dq200; соленоид регулятор давления dsg7 dq200; соленоид регулятор давления dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; соленоид регулятор давления dq200 дсг7; соленоид регулятор давления dq200 dsg 7; соленоид регулятор давления dq200 дсг 7; соленоид регулятор давления дсг7; соленоид регулятор давления dsg 7; соленоид регулятор давления дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7</t>
+          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; крышка мехатроника dq200 дсг7; крышка мехатроника dq200 dsg 7; крышка мехатроника dq200 дсг 7; крышка мехатроника дсг7; крышка мехатроника dsg 7; крышка мехатроника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>болт мехатроника dq200; болт мехатроника dsg7 dq200; болт мехатроника dsg7</t>
+          <t>болт мехатроника dq200; болт мехатроника dsg7 dq200; болт мехатроника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; болт мехатроника dq200 дсг7; болт мехатроника dq200 dsg 7; болт мехатроника dq200 дсг 7; болт мехатроника дсг7; болт мехатроника dsg 7; болт мехатроника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>болт мехатроника dq200; болт мехатроника dsg7 dq200; болт мехатроника dsg7</t>
+          <t>болт мехатроника dq200; болт мехатроника dsg7 dq200; болт мехатроника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; болт мехатроника dq200 дсг7; болт мехатроника dq200 dsg 7; болт мехатроника dq200 дсг 7; болт мехатроника дсг7; болт мехатроника dsg 7; болт мехатроника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>гидроплита dq200; гидроплита dsg7 dq200; гидроплита dsg7</t>
+          <t>гидроплита dq200; гидроплита dsg7 dq200; гидроплита dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; гидроплита dq200 дсг7; гидроплита dq200 dsg 7; гидроплита dq200 дсг 7; гидроплита дсг7; гидроплита dsg 7; гидроплита дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; плита dq200; плита dsg7; плита dsg7 dq200; плита мехатроника dq200; плита мехатроника dsg7 dq200; плита 0am; плита 0cw; гидроплита dq200; гидроплита dsg7; гидроплита dsg7 dq200; гидроплита мехатроника dq200; гидроплита мехатроника dsg7 dq200; усиленная плита dq200; усиленная гидроплита dq200; плита дсг7; гидроплита дсг7</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; плита dq200; плита dsg7; плита dsg7 dq200; плита мехатроника dq200; плита мехатроника dsg7 dq200; плита 0am; плита 0cw; гидроплита dq200; гидроплита dsg7; гидроплита dsg7 dq200; гидроплита мехатроника dq200; гидроплита мехатроника dsg7 dq200; усиленная плита dq200; усиленная гидроплита dq200; плита дсг7; гидроплита дсг7</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; плита dq200; плита dsg7; плита dsg7 dq200; плита мехатроника dq200; плита мехатроника dsg7 dq200; плита 0am; плита 0cw; гидроплита dq200; гидроплита dsg7; гидроплита dsg7 dq200; гидроплита мехатроника dq200; гидроплита мехатроника dsg7 dq200; усиленная плита dq200; усиленная гидроплита dq200; плита дсг7; гидроплита дсг7</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>фильтр dq500; фильтр dsg7 dq500</t>
+          <t>фильтр dq500; фильтр dsg7 dq500; прокладки dq500; прокладки dsg7; ремкомплект dq500; ремкомплект dsg7; запчасти мехатроника dq500; запчасти мехатроника dsg7; фильтр dq500 дсг7; фильтр dq500 dsg 7; фильтр dq500 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; плита dq200; плита dsg7; плита dsg7 dq200; плита мехатроника dq200; плита мехатроника dsg7 dq200; плита 0am; плита 0cw; гидроплита dq200; гидроплита dsg7; гидроплита dsg7 dq200; гидроплита мехатроника dq200; гидроплита мехатроника dsg7 dq200; усиленная плита dq200; усиленная гидроплита dq200; плита дсг7; гидроплита дсг7</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>корпус масляного фильтра dq250; корпус масляного фильтра dsg6 dq250</t>
+          <t>корпус масляного фильтра dq250; корпус масляного фильтра dsg6 dq250; прокладки dq250; прокладки dsg6; ремкомплект dq250; ремкомплект dsg6; запчасти мехатроника dq250; запчасти мехатроника dsg6; корпус масляного фильтра dq250 дсг6; корпус масляного фильтра dq250 dsg 6; корпус масляного фильтра dq250 дсг 6; прокладки дсг6; прокладки dsg 6; прокладки дсг 6; ремкомплект дсг6; ремкомплект dsg 6; ремкомплект дсг 6; запчасти мехатроника дсг6; запчасти мехатроника dsg 6; запчасти мехатроника дсг 6</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>корпус масляного фильтра dq250; корпус масляного фильтра dsg6 dq250</t>
+          <t>корпус масляного фильтра dq250; корпус масляного фильтра dsg6 dq250; прокладки dq250; прокладки dsg6; ремкомплект dq250; ремкомплект dsg6; запчасти мехатроника dq250; запчасти мехатроника dsg6; корпус масляного фильтра dq250 дсг6; корпус масляного фильтра dq250 dsg 6; корпус масляного фильтра dq250 дсг 6; прокладки дсг6; прокладки dsg 6; прокладки дсг 6; ремкомплект дсг6; ремкомплект dsg 6; ремкомплект дсг 6; запчасти мехатроника дсг6; запчасти мехатроника dsg 6; запчасти мехатроника дсг 6</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>корпус масляного фильтра dq500; корпус масляного фильтра dsg7 dq500</t>
+          <t>корпус масляного фильтра dq500; корпус масляного фильтра dsg7 dq500; прокладки dq500; прокладки dsg7; ремкомплект dq500; ремкомплект dsg7; запчасти мехатроника dq500; запчасти мехатроника dsg7; корпус масляного фильтра dq500 дсг7; корпус масляного фильтра dq500 dsg 7; корпус масляного фильтра dq500 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>шток dq200; шток dsg7 dq200; шток dsg7</t>
+          <t>шток dq200; шток dsg7 dq200; шток dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; шток dq200 дсг7; шток dq200 dsg 7; шток dq200 дсг 7; шток дсг7; шток dsg 7; шток дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>шток dq200; шток dsg7 dq200; шток dsg7</t>
+          <t>шток dq200; шток dsg7 dq200; шток dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; шток dq200 дсг7; шток dq200 dsg 7; шток dq200 дсг 7; шток дсг7; шток dsg 7; шток дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>планка соленоидов dq200; планка соленоидов dsg7 dq200; планка соленоидов dsg7</t>
+          <t>планка соленоидов dq200; планка соленоидов dsg7 dq200; планка соленоидов dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; планка соленоидов dq200 дсг7; планка соленоидов dq200 dsg 7; планка соленоидов dq200 дсг 7; планка соленоидов дсг7; планка соленоидов dsg 7; планка соленоидов дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7</t>
+          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сепараторная пластина dq200 дсг7; сепараторная пластина dq200 dsg 7; сепараторная пластина dq200 дсг 7; сепараторная пластина дсг7; сепараторная пластина dsg 7; сепараторная пластина дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7</t>
+          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сепараторная пластина dq200 дсг7; сепараторная пластина dq200 dsg 7; сепараторная пластина dq200 дсг 7; сепараторная пластина дсг7; сепараторная пластина dsg 7; сепараторная пластина дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7</t>
+          <t>сепараторная пластина dq200; сепараторная пластина dsg7 dq200; сепараторная пластина dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сепараторная пластина dq200 дсг7; сепараторная пластина dq200 dsg 7; сепараторная пластина dq200 дсг 7; сепараторная пластина дсг7; сепараторная пластина dsg 7; сепараторная пластина дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7</t>
+          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник dq200 дсг7; сальник dq200 dsg 7; сальник dq200 дсг 7; сальник дсг7; сальник dsg 7; сальник дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7</t>
+          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; крышка мехатроника dq200 дсг7; крышка мехатроника dq200 dsg 7; крышка мехатроника dq200 дсг 7; крышка мехатроника дсг7; крышка мехатроника dsg 7; крышка мехатроника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7</t>
+          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; крышка мехатроника dq200 дсг7; крышка мехатроника dq200 dsg 7; крышка мехатроника dq200 дсг 7; крышка мехатроника дсг7; крышка мехатроника dsg 7; крышка мехатроника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7</t>
+          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник dq200 дсг7; сальник dq200 dsg 7; сальник dq200 дсг 7; сальник дсг7; сальник dsg 7; сальник дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>фильтр-сетка dq500; фильтр-сетка dsg7 dq500</t>
+          <t>фильтр-сетка dq500; фильтр-сетка dsg7 dq500; прокладки dq500; прокладки dsg7; ремкомплект dq500; ремкомплект dsg7; запчасти мехатроника dq500; запчасти мехатроника dsg7; фильтр-сетка dq500 дсг7; фильтр-сетка dq500 dsg 7; фильтр-сетка dq500 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>клипса пыльника dq200; клипса пыльника dsg7 dq200; клипса пыльника dsg7</t>
+          <t>клипса пыльника dq200; клипса пыльника dsg7 dq200; клипса пыльника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; клипса пыльника dq200 дсг7; клипса пыльника dq200 dsg 7; клипса пыльника dq200 дсг 7; клипса пыльника дсг7; клипса пыльника dsg 7; клипса пыльника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7</t>
+          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; гидроаккумулятор dq200 дсг7; гидроаккумулятор dq200 dsg 7; гидроаккумулятор dq200 дсг 7; гидроаккумулятор дсг7; гидроаккумулятор dsg 7; гидроаккумулятор дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>фильтр-сетка dq500; фильтр-сетка dsg7 dq500</t>
+          <t>фильтр-сетка dq500; фильтр-сетка dsg7 dq500; прокладки dq500; прокладки dsg7; ремкомплект dq500; ремкомплект dsg7; запчасти мехатроника dq500; запчасти мехатроника dsg7; фильтр-сетка dq500 дсг7; фильтр-сетка dq500 dsg 7; фильтр-сетка dq500 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7</t>
+          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник dq200 дсг7; сальник dq200 dsg 7; сальник dq200 дсг 7; сальник дсг7; сальник dsg 7; сальник дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>корпус масляного фильтра dq250; корпус масляного фильтра dsg6 dq250</t>
+          <t>корпус масляного фильтра dq250; корпус масляного фильтра dsg6 dq250; прокладки dq250; прокладки dsg6; ремкомплект dq250; ремкомплект dsg6; запчасти мехатроника dq250; запчасти мехатроника dsg6; корпус масляного фильтра dq250 дсг6; корпус масляного фильтра dq250 dsg 6; корпус масляного фильтра dq250 дсг 6; прокладки дсг6; прокладки dsg 6; прокладки дсг 6; ремкомплект дсг6; ремкомплект dsg 6; ремкомплект дсг 6; запчасти мехатроника дсг6; запчасти мехатроника dsg 6; запчасти мехатроника дсг 6</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7</t>
+          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; эл. платы dq200 дсг7; эл. платы dq200 dsg 7; эл. платы dq200 дсг 7; эл. платы дсг7; эл. платы dsg 7; эл. платы дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7</t>
+          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; эл. платы dq200 дсг7; эл. платы dq200 dsg 7; эл. платы dq200 дсг 7; эл. платы дсг7; эл. платы dsg 7; эл. платы дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7</t>
+          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; эл. платы dq200 дсг7; эл. платы dq200 dsg 7; эл. платы dq200 дсг 7; эл. платы дсг7; эл. платы dsg 7; эл. платы дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7</t>
+          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; эл. платы dq200 дсг7; эл. платы dq200 dsg 7; эл. платы dq200 дсг 7; эл. платы дсг7; эл. платы dsg 7; эл. платы дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7</t>
+          <t>сальник dq200; сальник dsg7 dq200; сальник dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник dq200 дсг7; сальник dq200 dsg 7; сальник dq200 дсг 7; сальник дсг7; сальник dsg 7; сальник дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>планки соленоидов dq200; соленоиды на площадке dq200; группа соленоидов dq200; 122420A-EM; 122420A-AF; планки соленоидов dsg7 dq200; соленоиды на площадке dsg7 dq200; группа соленоидов dsg7 dq200; планки соленоидов dsg7; соленоиды на площадке dsg7; группа соленоидов dsg7</t>
+          <t>планки соленоидов dq200; соленоиды на площадке dq200; группа соленоидов dq200; 122420A-EM; 122420A-AF; планки соленоидов dsg7 dq200; соленоиды на площадке dsg7 dq200; группа соленоидов dsg7 dq200; планки соленоидов dsg7; соленоиды на площадке dsg7; группа соленоидов dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; планки соленоидов dq200 дсг7; планки соленоидов dq200 dsg 7; планки соленоидов dq200 дсг 7; соленоиды на площадке dq200 дсг7; соленоиды на площадке dq200 dsg 7; соленоиды на площадке dq200 дсг 7; группа соленоидов dq200 дсг7; группа соленоидов dq200 dsg 7; группа соленоидов dq200 дсг 7; планки соленоидов дсг7; планки соленоидов dsg 7; планки соленоидов дсг 7; соленоиды на площадке дсг7; соленоиды на площадке dsg 7; соленоиды на площадке дсг 7; группа соленоидов дсг7; группа соленоидов dsg 7; группа соленоидов дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>шток dq200; шток dsg7 dq200; шток dsg7</t>
+          <t>шток dq200; шток dsg7 dq200; шток dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; шток dq200 дсг7; шток dq200 dsg 7; шток dq200 дсг 7; шток дсг7; шток dsg 7; шток дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq250; мехатроник dsg6 dq250</t>
+          <t>мехатроник dq250; мехатроник dsg6 dq250; прокладки dq250; прокладки dsg6; ремкомплект dq250; ремкомплект dsg6; запчасти мехатроника dq250; запчасти мехатроника dsg6; мехатроник dq250 дсг6; мехатроник dq250 dsg 6; мехатроник dq250 дсг 6; прокладки дсг6; прокладки dsg 6; прокладки дсг 6; ремкомплект дсг6; ремкомплект dsg 6; ремкомплект дсг 6; запчасти мехатроника дсг6; запчасти мехатроника dsg 6; запчасти мехатроника дсг 6</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7</t>
+          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; гидроаккумулятор dq200 дсг7; гидроаккумулятор dq200 dsg 7; гидроаккумулятор dq200 дсг 7; гидроаккумулятор дсг7; гидроаккумулятор dsg 7; гидроаккумулятор дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7</t>
+          <t>крышка мехатроника dq200; крышка мехатроника dsg7 dq200; крышка мехатроника dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; крышка мехатроника dq200 дсг7; крышка мехатроника dq200 dsg 7; крышка мехатроника dq200 дсг 7; крышка мехатроника дсг7; крышка мехатроника dsg 7; крышка мехатроника дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>сальник привода левый dq200; сальник привода левый dsg7 dq200; сальник привода левый dsg7</t>
+          <t>сальник привода левый dq200; сальник привода левый dsg7 dq200; сальник привода левый dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник привода левый dq200 дсг7; сальник привода левый dq200 dsg 7; сальник привода левый dq200 дсг 7; сальник привода левый дсг7; сальник привода левый dsg 7; сальник привода левый дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>сальник привода правый dq200; сальник привода правый dsg7 dq200; сальник привода правый dsg7</t>
+          <t>сальник привода правый dq200; сальник привода правый dsg7 dq200; сальник привода правый dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник привода правый dq200 дсг7; сальник привода правый dq200 dsg 7; сальник привода правый dq200 дсг 7; сальник привода правый дсг7; сальник привода правый dsg 7; сальник привода правый дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>сальники dq200; сальники dsg7 dq200; сальники dsg7</t>
+          <t>сальники dq200; сальники dsg7 dq200; сальники dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальники dq200 дсг7; сальники dq200 dsg 7; сальники dq200 дсг 7; сальники дсг7; сальники dsg 7; сальники дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>сальник входного вала dq200; сальник входного вала dsg7 dq200; сальник входного вала dsg7</t>
+          <t>сальник входного вала dq200; сальник входного вала dsg7 dq200; сальник входного вала dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник входного вала dq200 дсг7; сальник входного вала dq200 dsg 7; сальник входного вала dq200 дсг 7; сальник входного вала дсг7; сальник входного вала dsg 7; сальник входного вала дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>сальник первичного вала dq200; сальник первичного вала dsg7 dq200; сальник первичного вала dsg7</t>
+          <t>сальник первичного вала dq200; сальник первичного вала dsg7 dq200; сальник первичного вала dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; сальник первичного вала dq200 дсг7; сальник первичного вала dq200 dsg 7; сальник первичного вала dq200 дсг 7; сальник первичного вала дсг7; сальник первичного вала dsg 7; сальник первичного вала дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>заглушка dq200; заглушка dsg7 dq200; заглушка dsg7</t>
+          <t>заглушка dq200; заглушка dsg7 dq200; заглушка dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; заглушка dq200 дсг7; заглушка dq200 dsg 7; заглушка dq200 дсг 7; заглушка дсг7; заглушка dsg 7; заглушка дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6 и задней передачи DSG7 DQ200</t>
+          <t>Подшипник вилки 6 и задней передачи DSG7 DQ200; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; Подшипник вилки 6 и задней передачи DQ200 дсг7; Подшипник вилки 6 и задней передачи DQ200 dsg 7; Подшипник вилки 6 и задней передачи DQ200 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6 и задней передачи DSG7 DQ200</t>
+          <t>Подшипник вилки 6 и задней передачи DSG7 DQ200; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; Подшипник вилки 6 и задней передачи DQ200 дсг7; Подшипник вилки 6 и задней передачи DQ200 dsg 7; Подшипник вилки 6 и задней передачи DQ200 дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>стальная вставка dq200; стальная вставка dsg7 dq200; стальная вставка dsg7</t>
+          <t>стальная вставка dq200; стальная вставка dsg7 dq200; стальная вставка dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; стальная вставка dq200 дсг7; стальная вставка dq200 dsg 7; стальная вставка dq200 дсг 7; стальная вставка дсг7; стальная вставка dsg 7; стальная вставка дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7</t>
+          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; гидроаккумулятор dq200 дсг7; гидроаккумулятор dq200 dsg 7; гидроаккумулятор dq200 дсг 7; гидроаккумулятор дсг7; гидроаккумулятор dsg 7; гидроаккумулятор дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7</t>
+          <t>гидроаккумулятор dq200; гидроаккумулятор dsg7 dq200; гидроаккумулятор dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; гидроаккумулятор dq200 дсг7; гидроаккумулятор dq200 dsg 7; гидроаккумулятор dq200 дсг 7; гидроаккумулятор дсг7; гидроаккумулятор dsg 7; гидроаккумулятор дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7</t>
+          <t>эл. платы dq200; эл. платы dsg7 dq200; эл. платы dsg7; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; эл. платы dq200 дсг7; эл. платы dq200 dsg 7; эл. платы dq200 дсг 7; эл. платы дсг7; эл. платы dsg 7; эл. платы дсг 7; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
         </is>
       </c>
     </row>

--- a/data/wordstat_queue.xlsx
+++ b/data/wordstat_queue.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; штоки dq200; штоки dsg7 dq200; штоки dsg7; штоки дсг7; штоки dsg 7; штоки дсг 7; втулка гильза штока dq200; втулка гильза штока dsg7 dq200; втулка гильза штока dsg7; втулка гильза штока дсг7; втулка гильза штока dsg 7; втулка гильза штока дсг 7; 0am325091E</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; шток dq200; шток dsg7 dq200; шток dsg7; шток дсг7; шток dsg 7; шток дсг 7; штоки dq200; штоки dsg7 dq200; штоки dsg7; штоки дсг7; штоки dsg 7; штоки дсг 7; втулка гильза штока dq200; втулка гильза штока dsg7 dq200; втулка гильза штока dsg7; втулка гильза штока дсг7; втулка гильза штока dsg 7; втулка гильза штока дсг 7; 0am325091F</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; мехатроник гидравлическая часть dq200; мехатроник гидравлическая часть dsg7 dq200; мехатроник гидравлическая часть dsg7; мехатроник гидравлическая часть дсг7; мехатроник гидравлическая часть dsg 7; мехатроник гидравлическая часть дсг 7; 0am325025</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; мехатроник с электронной платой dq200; мехатроник с электронной платой dsg7 dq200; мехатроник с электронной платой dsg7; мехатроник с электронной платой дсг7; мехатроник с электронной платой dsg 7; мехатроник с электронной платой дсг 7; мехатроник с платой dq200; мехатроник с платой dsg7 dq200; мехатроник с платой dsg7; мехатроник с платой дсг7; мехатроник с платой dsg 7; мехатроник с платой дсг 7; 0am325025</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; пластина на соленоиды dq200; пластина на соленоиды dsg7 dq200; пластина на соленоиды dsg7; пластина на соленоиды дсг7; пластина на соленоиды dsg 7; пластина на соленоиды дсг 7; пластины на соленоиды dq200; пластины на соленоиды dsg7 dq200; пластины на соленоиды dsg7; пластины на соленоиды дсг7; пластины на соленоиды dsg 7; пластины на соленоиды дсг 7</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; прокладка крышки dq200; прокладка крышки dsg7 dq200; прокладка крышки dsg7; прокладка крышки дсг7; прокладка крышки dsg 7; прокладка крышки дсг 7; прокладка крышки мехатроника dq200; прокладка крышки мехатроника dsg7 dq200; прокладка крышки мехатроника dsg7; прокладка крышки мехатроника дсг7; прокладка крышки мехатроника dsg 7; прокладка крышки мехатроника дсг 7; 0AM325443D</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; крышка штока dq200; крышка штока dsg7 dq200; крышка штока dsg7; крышка штока дсг7; крышка штока dsg 7; крышка штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальник штока dq200; сальник штока dsg7 dq200; сальник штока dsg7; сальник штока дсг7; сальник штока dsg 7; сальник штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; втулка гильза dq200; втулка гильза dsg7 dq200; втулка гильза dsg7; втулка гильза дсг7; втулка гильза dsg 7; втулка гильза дсг 7; втулка мехатроника dq200; втулка мехатроника dsg7 dq200; втулка мехатроника dsg7; втулка мехатроника дсг7; втулка мехатроника dsg 7; втулка мехатроника дсг 7; гильза мехатроника dq200; гильза мехатроника dsg7 dq200; гильза мехатроника dsg7; гильза мехатроника дсг7; гильза мехатроника dsg 7; гильза мехатроника дсг 7; втулка штока dq200; втулка штока dsg7 dq200; втулка штока dsg7; втулка штока дсг7; втулка штока dsg 7; втулка штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; ремкомплект штоков dq200; ремкомплект штоков dsg7 dq200; ремкомплект штоков dsg7; ремкомплект штоков дсг7; ремкомплект штоков dsg 7; ремкомплект штоков дсг 7; ремкомплект штока dq200; ремкомплект штока dsg7 dq200; ремкомплект штока dsg7; ремкомплект штока дсг7; ремкомплект штока dsg 7; ремкомплект штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальник штока dq200; сальник штока dsg7 dq200; сальник штока dsg7; сальник штока дсг7; сальник штока dsg 7; сальник штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; пыльник штока dq200; пыльник штока dsg7 dq200; пыльник штока dsg7; пыльник штока дсг7; пыльник штока dsg 7; пыльник штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальник штока dq200; сальник штока dsg7 dq200; сальник штока dsg7; сальник штока дсг7; сальник штока dsg 7; сальник штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; прокладки электронной платы dq200; прокладки электронной платы dsg7 dq200; прокладки электронной платы dsg7; прокладки электронной платы дсг7; прокладки электронной платы dsg 7; прокладки электронной платы дсг 7; прокладки эл платы dq200; прокладки эл платы dsg7 dq200; прокладки эл платы dsg7; прокладки эл платы дсг7; прокладки эл платы dsg 7; прокладки эл платы дсг 7; полный комплект прокладок платы dq200; полный комплект прокладок платы dsg7 dq200; полный комплект прокладок платы dsg7; полный комплект прокладок платы дсг7; полный комплект прокладок платы dsg 7; полный комплект прокладок платы дсг 7; 0AM927377</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; фильтр мехатроника dq200; фильтр мехатроника dsg7 dq200; фильтр мехатроника dsg7; фильтр мехатроника дсг7; фильтр мехатроника dsg 7; фильтр мехатроника дсг 7; масляный фильтр мехатроника dq200; масляный фильтр мехатроника dsg7 dq200; масляный фильтр мехатроника dsg7; масляный фильтр мехатроника дсг7; масляный фильтр мехатроника dsg 7; масляный фильтр мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальники толкателей вилок dq200; сальники толкателей вилок dsg7 dq200; сальники толкателей вилок dsg7; сальники толкателей вилок дсг7; сальники толкателей вилок dsg 7; сальники толкателей вилок дсг 7; толкатели вилок dq200; толкатели вилок dsg7 dq200; толкатели вилок dsg7; толкатели вилок дсг7; толкатели вилок dsg 7; толкатели вилок дсг 7</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; толкатели вилок dq200; толкатели вилок dsg7 dq200; толкатели вилок dsg7; толкатели вилок дсг7; толкатели вилок dsg 7; толкатели вилок дсг 7; сальники толкателей dq200; сальники толкателей dsg7 dq200; сальники толкателей dsg7; сальники толкателей дсг7; сальники толкателей dsg 7; сальники толкателей дсг 7; алюминиевые сальники толкателя dq200; алюминиевые сальники толкателя dsg7 dq200; алюминиевые сальники толкателя dsg7; алюминиевые сальники толкателя дсг7; алюминиевые сальники толкателя dsg 7; алюминиевые сальники толкателя дсг 7</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; толкатели вилок dq200; толкатели вилок dsg7 dq200; толкатели вилок dsg7; толкатели вилок дсг7; толкатели вилок dsg 7; толкатели вилок дсг 7; поршни мехатроника dq200; поршни мехатроника dsg7 dq200; поршни мехатроника dsg7; поршни мехатроника дсг7; поршни мехатроника dsg 7; поршни мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальники толкателей вилок dq200; сальники толкателей вилок dsg7 dq200; сальники толкателей вилок dsg7; сальники толкателей вилок дсг7; сальники толкателей вилок dsg 7; сальники толкателей вилок дсг 7; комплект сальников толкателей dq200; комплект сальников толкателей dsg7 dq200; комплект сальников толкателей dsg7; комплект сальников толкателей дсг7; комплект сальников толкателей dsg 7; комплект сальников толкателей дсг 7</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; алюминиевые сальники толкателя dq200; алюминиевые сальники толкателя dsg7 dq200; алюминиевые сальники толкателя dsg7; алюминиевые сальники толкателя дсг7; алюминиевые сальники толкателя dsg 7; алюминиевые сальники толкателя дсг 7; сальники толкателя dq200; сальники толкателя dsg7 dq200; сальники толкателя dsg7; сальники толкателя дсг7; сальники толкателя dsg 7; сальники толкателя дсг 7</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; болты мехатроника dq200; болты мехатроника dsg7 dq200; болты мехатроника dsg7; болты мехатроника дсг7; болты мехатроника dsg 7; болты мехатроника дсг 7; комплект болтов dq200; комплект болтов dsg7 dq200; комплект болтов dsg7; комплект болтов дсг7; комплект болтов dsg 7; комплект болтов дсг 7; болты крепления мехатроника dq200; болты крепления мехатроника dsg7 dq200; болты крепления мехатроника dsg7; болты крепления мехатроника дсг7; болты крепления мехатроника dsg 7; болты крепления мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальники штоков dq200; сальники штоков dsg7 dq200; сальники штоков dsg7; сальники штоков дсг7; сальники штоков dsg 7; сальники штоков дсг 7</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; фильтр мехатроника dq200; фильтр мехатроника dsg7 dq200; фильтр мехатроника dsg7; фильтр мехатроника дсг7; фильтр мехатроника dsg 7; фильтр мехатроника дсг 7; масляный фильтр мехатроника dq200; масляный фильтр мехатроника dsg7 dq200; масляный фильтр мехатроника dsg7; масляный фильтр мехатроника дсг7; масляный фильтр мехатроника dsg 7; масляный фильтр мехатроника дсг 7</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; клипсы штоков dq200; клипсы штоков dsg7 dq200; клипсы штоков dsg7; клипсы штоков дсг7; клипсы штоков dsg 7; клипсы штоков дсг 7; фиксаторы штоков dq200; фиксаторы штоков dsg7 dq200; фиксаторы штоков dsg7; фиксаторы штоков дсг7; фиксаторы штоков dsg 7; фиксаторы штоков дсг 7</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; мехатроник с электронной платой dq200; мехатроник с электронной платой dsg7 dq200; мехатроник с электронной платой dsg7; мехатроник с электронной платой дсг7; мехатроник с электронной платой dsg 7; мехатроник с электронной платой дсг 7; мехатроник с платой dq200; мехатроник с платой dsg7 dq200; мехатроник с платой dsg7; мехатроник с платой дсг7; мехатроник с платой dsg 7; мехатроник с платой дсг 7; мехатроник проверенный dq200; мехатроник проверенный dsg7 dq200; мехатроник проверенный dsg7; мехатроник проверенный дсг7; мехатроник проверенный dsg 7; мехатроник проверенный дсг 7</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; пыльники штоков dq200; пыльники штоков dsg7 dq200; пыльники штоков dsg7; пыльники штоков дсг7; пыльники штоков dsg 7; пыльники штоков дсг 7; пыльник штока dq200; пыльник штока dsg7 dq200; пыльник штока dsg7; пыльник штока дсг7; пыльник штока dsg 7; пыльник штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; сальники штоков dq200; сальники штоков dsg7 dq200; сальники штоков dsg7; сальники штоков дсг7; сальники штоков dsg 7; сальники штоков дсг 7; сальник штока dq200; сальник штока dsg7 dq200; сальник штока dsg7; сальник штока дсг7; сальник штока dsg 7; сальник штока дсг 7</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7</t>
+          <t>мехатроник dq200; мехатроник dsg7 dq200; мехатроник dsg7; мехатроник 0am; мехатроник 0cw; прокладки dq200; прокладки dsg7; ремкомплект dq200; ремкомплект dsg7; запчасти мехатроника dq200; запчасти мехатроника dsg7; мехатроник dq200 дсг7; мехатроник dq200 dsg 7; мехатроник dq200 дсг 7; мехатроник дсг7; мехатроник dsg 7; мехатроник дсг 7; мехатроник 0ам; прокладки дсг7; прокладки dsg 7; прокладки дсг 7; ремкомплект дсг7; ремкомплект dsg 7; ремкомплект дсг 7; запчасти мехатроника дсг7; запчасти мехатроника dsg 7; запчасти мехатроника дсг 7; прокладка мехатроника dq200; прокладка мехатроника dsg7 dq200; прокладка мехатроника dsg7; прокладка мехатроника дсг7; прокладка мехатроника dsg 7; прокладка мехатроника дсг 7; прокладки мехатроника dq200; прокладки мехатроника dsg7 dq200; прокладки мехатроника dsg7; прокладки мехатроника дсг7; прокладки мехатроника dsg 7; прокладки мехатроника дсг 7</t>
         </is>
       </c>
     </row>
